--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -490,6 +490,19 @@
   </si>
   <si>
     <t>This is a modifier role that can hold a role and a reference to the item who has the role. Ex. owner + a reference to the owner organization.</t>
+  </si>
+  <si>
+    <t>Library.extension:aggregationMode</t>
+  </si>
+  <si>
+    <t>aggregationMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-aggregation-mode}
+</t>
+  </si>
+  <si>
+    <t>Mode of Aggregated Triage</t>
   </si>
   <si>
     <t>Library.modifierExtension</t>
@@ -721,7 +734,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the library content is focused on</t>
@@ -739,7 +752,7 @@
     <t>The possible types of subjects for a library (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Library.date</t>
@@ -914,7 +927,7 @@
   </si>
   <si>
     <t>CodeableConcept
-QuantityRangeReference(PlanDefinition|ResearchStudy|InsurancePlan|HealthcareService|Group|Location|Organization)</t>
+QuantityRangeReference(PlanDefinition|4.0.1|ResearchStudy|4.0.1|InsurancePlan|4.0.1|HealthcareService|4.0.1|Group|4.0.1|Location|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
     <t>Value that defines the context</t>
@@ -929,7 +942,7 @@
     <t>A code that defines the specific value for the context being specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/use-context</t>
+    <t>http://hl7.org/fhir/ValueSet/use-context|4.0.1</t>
   </si>
   <si>
     <t>UsageContext.value[x]</t>
@@ -1082,7 +1095,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>Library.author</t>
@@ -1483,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="29.38671875" customWidth="true" bestFit="true"/>
@@ -1496,7 +1509,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.97265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="126.671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2900,43 +2913,41 @@
         <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>75</v>
       </c>
@@ -2984,7 +2995,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2993,13 +3004,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>136</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3013,45 +3024,45 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -3100,28 +3111,28 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>75</v>
@@ -3129,10 +3140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3143,7 +3154,7 @@
         <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>75</v>
@@ -3155,19 +3166,19 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>75</v>
@@ -3216,13 +3227,13 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>75</v>
@@ -3231,24 +3242,24 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>176</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3256,10 +3267,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>75</v>
@@ -3271,18 +3282,20 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
       </c>
@@ -3330,13 +3343,13 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>75</v>
@@ -3345,24 +3358,24 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3370,7 +3383,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>84</v>
@@ -3385,20 +3398,18 @@
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>75</v>
       </c>
@@ -3446,7 +3457,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3455,19 +3466,19 @@
         <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
@@ -3475,10 +3486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3501,18 +3512,20 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
       </c>
@@ -3560,7 +3573,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3569,16 +3582,16 @@
         <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>75</v>
@@ -3589,10 +3602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3612,18 +3625,20 @@
         <v>75</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3672,7 +3687,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3687,10 +3702,10 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>75</v>
@@ -3701,10 +3716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3712,7 +3727,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>84</v>
@@ -3721,23 +3736,21 @@
         <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>203</v>
       </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3762,13 +3775,13 @@
         <v>75</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -3786,10 +3799,10 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>84</v>
@@ -3801,13 +3814,13 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>75</v>
@@ -3815,10 +3828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3826,7 +3839,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>84</v>
@@ -3835,26 +3848,24 @@
         <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
       </c>
@@ -3878,13 +3889,13 @@
         <v>75</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -3902,10 +3913,10 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>84</v>
@@ -3917,13 +3928,13 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>75</v>
@@ -3931,10 +3942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3942,7 +3953,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>84</v>
@@ -3957,16 +3968,20 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
       </c>
@@ -3990,11 +4005,13 @@
         <v>75</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>222</v>
+        <v>75</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>75</v>
@@ -4012,10 +4029,10 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>84</v>
@@ -4027,13 +4044,13 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>75</v>
@@ -4041,10 +4058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4052,7 +4069,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
@@ -4064,25 +4081,23 @@
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>75</v>
       </c>
@@ -4102,13 +4117,11 @@
         <v>75</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>75</v>
@@ -4126,10 +4139,10 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>84</v>
@@ -4141,13 +4154,13 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>75</v>
@@ -4155,14 +4168,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4178,25 +4191,25 @@
         <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>75</v>
       </c>
@@ -4216,13 +4229,13 @@
         <v>75</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -4240,7 +4253,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4255,13 +4268,13 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>75</v>
@@ -4269,14 +4282,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4295,20 +4308,18 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4356,7 +4367,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4371,13 +4382,13 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>75</v>
@@ -4385,10 +4396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4399,7 +4410,7 @@
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4411,18 +4422,20 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>182</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4470,13 +4483,13 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>75</v>
@@ -4485,13 +4498,13 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>75</v>
+        <v>253</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>75</v>
@@ -4499,10 +4512,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4513,7 +4526,7 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4525,16 +4538,16 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4584,13 +4597,13 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>75</v>
@@ -4599,10 +4612,10 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>75</v>
@@ -4613,10 +4626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4627,7 +4640,7 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>75</v>
@@ -4639,20 +4652,18 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>269</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4700,13 +4711,13 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>75</v>
@@ -4715,10 +4726,10 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>182</v>
+        <v>266</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>75</v>
@@ -4729,10 +4740,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4743,7 +4754,7 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4752,19 +4763,23 @@
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4812,25 +4827,25 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>75</v>
@@ -4841,21 +4856,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -4867,17 +4882,15 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4914,34 +4927,34 @@
         <v>75</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AC30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4955,21 +4968,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -4978,18 +4991,20 @@
         <v>75</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N31" s="2"/>
+      <c r="N31" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -5014,44 +5029,46 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>75</v>
+        <v>283</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>75</v>
@@ -5065,10 +5082,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5091,13 +5108,13 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5124,13 +5141,11 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -5148,7 +5163,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -5177,10 +5192,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5188,10 +5203,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -5203,17 +5218,15 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>219</v>
+        <v>292</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5238,11 +5251,13 @@
         <v>75</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5260,13 +5275,13 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
@@ -5275,10 +5290,10 @@
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>75</v>
@@ -5289,10 +5304,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5303,7 +5318,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -5312,19 +5327,19 @@
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5350,13 +5365,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5374,13 +5387,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -5389,24 +5402,24 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>186</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>75</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>176</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5429,15 +5442,17 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>262</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5486,7 +5501,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5501,28 +5516,28 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>182</v>
+        <v>309</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>312</v>
+        <v>75</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5541,7 +5556,7 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>313</v>
@@ -5550,9 +5565,7 @@
         <v>314</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -5600,7 +5613,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5615,28 +5628,28 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>75</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>176</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>316</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5655,18 +5668,18 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
@@ -5714,7 +5727,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5729,24 +5742,24 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5769,20 +5782,18 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>328</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5830,7 +5841,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5845,24 +5856,24 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5882,22 +5893,22 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5946,7 +5957,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5961,24 +5972,24 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5989,7 +6000,7 @@
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -5998,20 +6009,22 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>219</v>
+        <v>336</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6036,13 +6049,13 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>342</v>
+        <v>75</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>343</v>
+        <v>75</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>75</v>
@@ -6060,13 +6073,13 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
@@ -6075,24 +6088,24 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6115,16 +6128,18 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6148,13 +6163,13 @@
         <v>75</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>75</v>
+        <v>347</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -6172,7 +6187,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6187,7 +6202,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>347</v>
+        <v>186</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6227,7 +6242,7 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>349</v>
@@ -6299,7 +6314,7 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>75</v>
+        <v>351</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6313,10 +6328,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6339,13 +6354,13 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6396,7 +6411,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6411,7 +6426,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6451,7 +6466,7 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>356</v>
@@ -6523,7 +6538,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6537,10 +6552,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6563,7 +6578,7 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>359</v>
+        <v>255</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>360</v>
@@ -6571,12 +6586,8 @@
       <c r="M45" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>363</v>
-      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6624,7 +6635,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6639,7 +6650,7 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6653,10 +6664,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6664,7 +6675,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>77</v>
@@ -6679,16 +6690,20 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -6736,7 +6751,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6751,7 +6766,7 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>182</v>
+        <v>368</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6776,7 +6791,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>77</v>
@@ -6863,7 +6878,7 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6900,7 +6915,7 @@
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>374</v>
@@ -6975,7 +6990,7 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>262</v>
+        <v>186</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6984,6 +6999,118 @@
         <v>75</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>75</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-library.xlsx
+++ b/fhir/StructureDefinition-ehealth-library.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
